--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" refreshedBy="Jan Havlíček" refreshedDate="45204.858940393518" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{99F3BC45-6F88-410F-AAEB-E251F2194064}" mc:Ignorable="xr">
+<x:pivotCacheDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="0" refreshedBy="Jan Havlíček" refreshedDate="45204.858940393518" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{99F3BC45-6F88-410F-AAEB-E251F2194064}" mc:Ignorable="xr">
   <x:cacheSource type="worksheet">
     <x:worksheetSource name="Table1"/>
   </x:cacheSource>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
@@ -40,7 +40,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>Row Labels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum of Sold</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pie</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Total</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -495,7 +511,40 @@
     <x:col min="1" max="1" width="13.140625" style="0" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="11.425781" style="0" bestFit="1" customWidth="1"/>
   </x:cols>
-  <x:sheetData/>
+  <x:sheetData>
+    <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A3" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A4" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A5" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <x:c r="A6" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
@@ -196,7 +196,7 @@
   <dataFields count="1">
     <dataField name="Sum of Sold" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
